--- a/grupos/5ARHV - Estadisticos 20231.xlsx
+++ b/grupos/5ARHV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="88">
   <si>
     <t>Materia</t>
   </si>
@@ -170,24 +170,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
+    <t>González Nuñez Veronica</t>
   </si>
   <si>
     <t>Saucedo Rivalcoba Liliana Guadalupe</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -206,16 +206,28 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
     <t>HERRERA</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>VEGA</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>TLAXCALTECATL</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
   </si>
   <si>
     <t>ARIAS</t>
@@ -224,16 +236,22 @@
     <t>CELESTINO</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>SIERRA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
   </si>
   <si>
     <t>ALESSANDRA</t>
@@ -242,16 +260,28 @@
     <t>KARLA JIMENA</t>
   </si>
   <si>
+    <t>INGRID CRISTEL</t>
+  </si>
+  <si>
+    <t>YAZURI</t>
+  </si>
+  <si>
+    <t>GABRIELA ELIZABET</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
     <t>MIA ARANZA</t>
   </si>
   <si>
-    <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>YAZURI</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
+    <t>MICHEL</t>
+  </si>
+  <si>
+    <t>KARLA JAZMIN</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
   </si>
 </sst>
 </file>
@@ -759,22 +789,22 @@
         <v>4</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -801,10 +831,10 @@
         <v>5</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -836,22 +866,22 @@
         <v>7</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -878,13 +908,13 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -913,22 +943,22 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -958,10 +988,10 @@
         <v>6</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -990,22 +1020,22 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1026,19 +1056,19 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U7">
         <v>10</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1067,22 +1097,22 @@
         <v>5</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1103,22 +1133,22 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>5</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1144,22 +1174,22 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1186,13 +1216,13 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>8</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1221,22 +1251,22 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1257,22 +1287,22 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1298,22 +1328,22 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1340,16 +1370,16 @@
         <v>9</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1375,22 +1405,22 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1414,19 +1444,19 @@
         <v>9</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1452,22 +1482,22 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1491,13 +1521,13 @@
         <v>9</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>7</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>8</v>
@@ -1529,22 +1559,22 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1571,13 +1601,13 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>10</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1606,22 +1636,22 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1642,19 +1672,19 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>7</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1683,22 +1713,22 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1725,16 +1755,16 @@
         <v>7</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1760,22 +1790,22 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1802,13 +1832,13 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>8</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -1837,22 +1867,22 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1873,22 +1903,22 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1914,22 +1944,22 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1953,13 +1983,13 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -1991,22 +2021,22 @@
         <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2027,7 +2057,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2036,10 +2066,10 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2068,22 +2098,22 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2107,19 +2137,19 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>8</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2145,22 +2175,22 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2184,19 +2214,19 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2222,22 +2252,22 @@
         <v>9</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2258,19 +2288,19 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>7</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>9</v>
@@ -2299,22 +2329,22 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2341,16 +2371,16 @@
         <v>6</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2376,22 +2406,22 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2415,16 +2445,16 @@
         <v>9</v>
       </c>
       <c r="U25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>8</v>
@@ -2453,22 +2483,22 @@
         <v>7</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2495,13 +2525,13 @@
         <v>5</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>7</v>
@@ -2530,22 +2560,22 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2572,13 +2602,13 @@
         <v>6</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2607,22 +2637,22 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2649,16 +2679,16 @@
         <v>8</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>5</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2684,22 +2714,22 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2720,22 +2750,22 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>6</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2871,40 +2901,40 @@
         <v>86.7</v>
       </c>
       <c r="H4">
+        <v>72.5</v>
+      </c>
+      <c r="I4">
+        <v>94</v>
+      </c>
+      <c r="J4">
         <v>85</v>
       </c>
-      <c r="I4">
-        <v>100</v>
-      </c>
-      <c r="J4">
-        <v>90</v>
-      </c>
       <c r="K4">
         <v>100</v>
       </c>
       <c r="L4">
-        <v>86.7</v>
+        <v>91.5</v>
       </c>
       <c r="M4">
-        <v>86.7</v>
+        <v>78.3</v>
       </c>
       <c r="N4">
+        <v>72.5</v>
+      </c>
+      <c r="O4">
+        <v>94</v>
+      </c>
+      <c r="P4">
         <v>85</v>
       </c>
-      <c r="O4">
-        <v>100</v>
-      </c>
-      <c r="P4">
-        <v>90</v>
-      </c>
       <c r="Q4">
         <v>100</v>
       </c>
       <c r="R4">
-        <v>86.7</v>
+        <v>91.5</v>
       </c>
       <c r="S4">
-        <v>86.7</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2930,7 +2960,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="I5">
         <v>100</v>
@@ -2939,16 +2969,16 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L5">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="M5">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="N5">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -2957,13 +2987,13 @@
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R5">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2989,40 +3019,40 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I6">
         <v>100</v>
       </c>
       <c r="J6">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="K6">
         <v>100</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O6">
         <v>100</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="Q6">
         <v>100</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3048,37 +3078,37 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="I7">
         <v>100</v>
       </c>
       <c r="J7">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K7">
         <v>100</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="M7">
         <v>100</v>
       </c>
       <c r="N7">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -3107,7 +3137,7 @@
         <v>93.3</v>
       </c>
       <c r="H8">
-        <v>80</v>
+        <v>77.5</v>
       </c>
       <c r="I8">
         <v>100</v>
@@ -3119,13 +3149,13 @@
         <v>100</v>
       </c>
       <c r="L8">
-        <v>76.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="M8">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="N8">
-        <v>80</v>
+        <v>77.5</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -3137,10 +3167,10 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>76.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="S8">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3166,7 +3196,7 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="I9">
         <v>100</v>
@@ -3178,13 +3208,13 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N9">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -3196,10 +3226,10 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S9">
-        <v>100</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3225,7 +3255,7 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="I10">
         <v>100</v>
@@ -3237,13 +3267,13 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="M10">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -3255,10 +3285,10 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3284,7 +3314,7 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I11">
         <v>100</v>
@@ -3296,13 +3326,13 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="M11">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -3314,10 +3344,10 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3343,40 +3373,40 @@
         <v>93.3</v>
       </c>
       <c r="H12">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I12">
         <v>100</v>
       </c>
       <c r="J12">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12">
+        <v>89.8</v>
+      </c>
+      <c r="M12">
         <v>83.3</v>
       </c>
-      <c r="M12">
-        <v>93.3</v>
-      </c>
       <c r="N12">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
+        <v>89.8</v>
+      </c>
+      <c r="S12">
         <v>83.3</v>
-      </c>
-      <c r="S12">
-        <v>93.3</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3402,40 +3432,40 @@
         <v>100</v>
       </c>
       <c r="H13">
+        <v>85</v>
+      </c>
+      <c r="I13">
+        <v>100</v>
+      </c>
+      <c r="J13">
+        <v>100</v>
+      </c>
+      <c r="K13">
+        <v>100</v>
+      </c>
+      <c r="L13">
+        <v>98.3</v>
+      </c>
+      <c r="M13">
         <v>95</v>
       </c>
-      <c r="I13">
-        <v>100</v>
-      </c>
-      <c r="J13">
-        <v>100</v>
-      </c>
-      <c r="K13">
-        <v>100</v>
-      </c>
-      <c r="L13">
-        <v>100</v>
-      </c>
-      <c r="M13">
-        <v>100</v>
-      </c>
       <c r="N13">
+        <v>85</v>
+      </c>
+      <c r="O13">
+        <v>100</v>
+      </c>
+      <c r="P13">
+        <v>100</v>
+      </c>
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
+        <v>98.3</v>
+      </c>
+      <c r="S13">
         <v>95</v>
-      </c>
-      <c r="O13">
-        <v>100</v>
-      </c>
-      <c r="P13">
-        <v>100</v>
-      </c>
-      <c r="Q13">
-        <v>100</v>
-      </c>
-      <c r="R13">
-        <v>100</v>
-      </c>
-      <c r="S13">
-        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3461,7 +3491,7 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="I14">
         <v>100</v>
@@ -3479,7 +3509,7 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -3520,40 +3550,40 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="I15">
         <v>100</v>
       </c>
       <c r="J15">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K15">
         <v>100</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="M15">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="N15">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="O15">
         <v>100</v>
       </c>
       <c r="P15">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q15">
         <v>100</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="S15">
-        <v>100</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3579,40 +3609,40 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I16">
         <v>100</v>
       </c>
       <c r="J16">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="K16">
         <v>100</v>
       </c>
       <c r="L16">
-        <v>86.7</v>
+        <v>89.8</v>
       </c>
       <c r="M16">
-        <v>100</v>
+        <v>88.3</v>
       </c>
       <c r="N16">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="O16">
         <v>100</v>
       </c>
       <c r="P16">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="Q16">
         <v>100</v>
       </c>
       <c r="R16">
-        <v>86.7</v>
+        <v>89.8</v>
       </c>
       <c r="S16">
-        <v>100</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3638,13 +3668,13 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I17">
         <v>100</v>
       </c>
       <c r="J17">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K17">
         <v>100</v>
@@ -3653,16 +3683,16 @@
         <v>100</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="N17">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -3671,7 +3701,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>100</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3697,7 +3727,7 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="I18">
         <v>100</v>
@@ -3709,13 +3739,13 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>96.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="M18">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="N18">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -3727,10 +3757,10 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>96.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3756,37 +3786,37 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I19">
         <v>100</v>
       </c>
       <c r="J19">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K19">
         <v>100</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="M19">
         <v>100</v>
       </c>
       <c r="N19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O19">
         <v>100</v>
       </c>
       <c r="P19">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -3815,7 +3845,7 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I20">
         <v>100</v>
@@ -3827,13 +3857,13 @@
         <v>100</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="M20">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N20">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -3845,10 +3875,10 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3933,7 +3963,7 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I22">
         <v>100</v>
@@ -3945,13 +3975,13 @@
         <v>100</v>
       </c>
       <c r="L22">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="M22">
         <v>100</v>
       </c>
       <c r="N22">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O22">
         <v>100</v>
@@ -3963,7 +3993,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -3992,16 +4022,16 @@
         <v>100</v>
       </c>
       <c r="H23">
+        <v>92.5</v>
+      </c>
+      <c r="I23">
+        <v>100</v>
+      </c>
+      <c r="J23">
         <v>95</v>
       </c>
-      <c r="I23">
-        <v>100</v>
-      </c>
-      <c r="J23">
-        <v>90</v>
-      </c>
       <c r="K23">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -4010,16 +4040,16 @@
         <v>100</v>
       </c>
       <c r="N23">
+        <v>92.5</v>
+      </c>
+      <c r="O23">
+        <v>100</v>
+      </c>
+      <c r="P23">
         <v>95</v>
       </c>
-      <c r="O23">
-        <v>100</v>
-      </c>
-      <c r="P23">
-        <v>90</v>
-      </c>
       <c r="Q23">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -4051,40 +4081,40 @@
         <v>100</v>
       </c>
       <c r="H24">
+        <v>87.5</v>
+      </c>
+      <c r="I24">
+        <v>100</v>
+      </c>
+      <c r="J24">
+        <v>100</v>
+      </c>
+      <c r="K24">
+        <v>100</v>
+      </c>
+      <c r="L24">
+        <v>93.2</v>
+      </c>
+      <c r="M24">
         <v>95</v>
       </c>
-      <c r="I24">
-        <v>100</v>
-      </c>
-      <c r="J24">
-        <v>100</v>
-      </c>
-      <c r="K24">
-        <v>100</v>
-      </c>
-      <c r="L24">
-        <v>96.7</v>
-      </c>
-      <c r="M24">
-        <v>100</v>
-      </c>
       <c r="N24">
+        <v>87.5</v>
+      </c>
+      <c r="O24">
+        <v>100</v>
+      </c>
+      <c r="P24">
+        <v>100</v>
+      </c>
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
+        <v>93.2</v>
+      </c>
+      <c r="S24">
         <v>95</v>
-      </c>
-      <c r="O24">
-        <v>100</v>
-      </c>
-      <c r="P24">
-        <v>100</v>
-      </c>
-      <c r="Q24">
-        <v>100</v>
-      </c>
-      <c r="R24">
-        <v>96.7</v>
-      </c>
-      <c r="S24">
-        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4110,37 +4140,37 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="I25">
         <v>100</v>
       </c>
       <c r="J25">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L25">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="M25">
         <v>100</v>
       </c>
       <c r="N25">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R25">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -4169,7 +4199,7 @@
         <v>100</v>
       </c>
       <c r="H26">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I26">
         <v>100</v>
@@ -4178,16 +4208,16 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N26">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -4196,13 +4226,13 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R26">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4228,7 +4258,7 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I27">
         <v>100</v>
@@ -4243,10 +4273,10 @@
         <v>100</v>
       </c>
       <c r="M27">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N27">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O27">
         <v>100</v>
@@ -4261,7 +4291,7 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4287,40 +4317,40 @@
         <v>90</v>
       </c>
       <c r="H28">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="I28">
         <v>100</v>
       </c>
       <c r="J28">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="K28">
         <v>100</v>
       </c>
       <c r="L28">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="M28">
-        <v>90</v>
+        <v>78.3</v>
       </c>
       <c r="N28">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="O28">
         <v>100</v>
       </c>
       <c r="P28">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="Q28">
         <v>100</v>
       </c>
       <c r="R28">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="S28">
-        <v>90</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4346,7 +4376,7 @@
         <v>83.3</v>
       </c>
       <c r="H29">
-        <v>85</v>
+        <v>72.5</v>
       </c>
       <c r="I29">
         <v>100</v>
@@ -4358,13 +4388,13 @@
         <v>100</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="M29">
-        <v>83.3</v>
+        <v>86.7</v>
       </c>
       <c r="N29">
-        <v>85</v>
+        <v>72.5</v>
       </c>
       <c r="O29">
         <v>100</v>
@@ -4376,10 +4406,10 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="S29">
-        <v>83.3</v>
+        <v>86.7</v>
       </c>
     </row>
   </sheetData>
@@ -4436,7 +4466,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>50</v>
@@ -4445,19 +4475,19 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>80.8</v>
+        <v>61.5</v>
       </c>
       <c r="G2" s="2">
-        <v>19.2</v>
+        <v>38.5</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4468,7 +4498,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
@@ -4477,19 +4507,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>88.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>11.5</v>
+        <v>15.4</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4500,7 +4530,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
@@ -4509,19 +4539,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>92.3</v>
+        <v>88.5</v>
       </c>
       <c r="G4" s="2">
-        <v>7.7</v>
+        <v>11.5</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4532,7 +4562,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
@@ -4541,19 +4571,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>96.2</v>
+        <v>88.5</v>
       </c>
       <c r="G5" s="2">
-        <v>3.8</v>
+        <v>11.5</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4585,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4596,7 +4626,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -4617,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4667,7 +4697,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4705,16 +4735,16 @@
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4728,16 +4758,16 @@
         <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4751,16 +4781,16 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4768,22 +4798,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920046</v>
+        <v>21330051920390</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4794,16 +4824,16 @@
         <v>21330051920057</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>50</v>
@@ -4814,19 +4844,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920063</v>
+        <v>21330051920057</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>51</v>
@@ -4837,24 +4867,185 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920067</v>
+        <v>21330051920063</v>
       </c>
       <c r="B8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920063</v>
+      </c>
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920035</v>
+      </c>
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920036</v>
+      </c>
+      <c r="B11" t="s">
         <v>65</v>
       </c>
-      <c r="C8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920046</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920048</v>
+      </c>
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920062</v>
+      </c>
+      <c r="B14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920065</v>
+      </c>
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" t="s">
         <v>77</v>
       </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="D15" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
         <v>50</v>
       </c>
-      <c r="G8">
+      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHV - Estadisticos 20231.xlsx
+++ b/grupos/5ARHV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="83">
   <si>
     <t>Materia</t>
   </si>
@@ -173,21 +173,21 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
+    <t>Saucedo Rivalcoba Liliana Guadalupe</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Saucedo Rivalcoba Liliana Guadalupe</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -200,48 +200,33 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>TLAXCALTECATL</t>
+    <t>ROMANOS</t>
   </si>
   <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>CELESTINO</t>
+    <t>VEGA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -251,37 +236,37 @@
     <t>JIMENEZ</t>
   </si>
   <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
     <t>GALEOTE</t>
   </si>
   <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>KARLA JIMENA</t>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>GABRIELA ELIZABET</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>MIA ARANZA</t>
+  </si>
+  <si>
+    <t>MICHEL</t>
   </si>
   <si>
     <t>INGRID CRISTEL</t>
   </si>
   <si>
-    <t>YAZURI</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABET</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>MICHEL</t>
-  </si>
-  <si>
-    <t>KARLA JAZMIN</t>
+    <t>DANIELA</t>
   </si>
   <si>
     <t>XIMENA</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
   </si>
 </sst>
 </file>
@@ -807,28 +792,28 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>9</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>6</v>
@@ -837,10 +822,10 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -884,22 +869,22 @@
         <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -949,7 +934,7 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -961,22 +946,22 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -985,7 +970,7 @@
         <v>6</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1038,25 +1023,25 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>10</v>
@@ -1115,25 +1100,25 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U8">
         <v>5</v>
@@ -1148,7 +1133,7 @@
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1192,22 +1177,22 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>9</v>
@@ -1225,7 +1210,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1269,28 +1254,28 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>8</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -1299,7 +1284,7 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1346,22 +1331,22 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1379,7 +1364,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1423,28 +1408,28 @@
         <v>4</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>9</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>7</v>
@@ -1453,10 +1438,10 @@
         <v>8</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1488,7 +1473,7 @@
         <v>8</v>
       </c>
       <c r="J13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>8</v>
@@ -1500,22 +1485,22 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1565,7 +1550,7 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K14">
         <v>10</v>
@@ -1577,22 +1562,22 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1601,13 +1586,13 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>10</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1654,22 +1639,22 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1731,22 +1716,22 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1764,7 +1749,7 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1796,7 +1781,7 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K17">
         <v>8</v>
@@ -1808,22 +1793,22 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -1832,13 +1817,13 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>8</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -1885,28 +1870,28 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>7</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -1918,7 +1903,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1950,7 +1935,7 @@
         <v>9</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>9</v>
@@ -1962,31 +1947,31 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>10</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2039,22 +2024,22 @@
         <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2069,10 +2054,10 @@
         <v>8</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2104,7 +2089,7 @@
         <v>9</v>
       </c>
       <c r="J21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K21">
         <v>9</v>
@@ -2116,22 +2101,22 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2181,7 +2166,7 @@
         <v>9</v>
       </c>
       <c r="J22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K22">
         <v>9</v>
@@ -2193,22 +2178,22 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2270,28 +2255,28 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>8</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -2300,7 +2285,7 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>9</v>
@@ -2347,22 +2332,22 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>8</v>
@@ -2380,7 +2365,7 @@
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2424,22 +2409,22 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2489,7 +2474,7 @@
         <v>6</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>9</v>
@@ -2501,31 +2486,31 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>9</v>
       </c>
       <c r="U26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2534,7 +2519,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2566,7 +2551,7 @@
         <v>6</v>
       </c>
       <c r="J27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>9</v>
@@ -2578,31 +2563,31 @@
         <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>9</v>
       </c>
       <c r="U27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -2655,28 +2640,28 @@
         <v>4</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>9</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>5</v>
@@ -2685,10 +2670,10 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2732,28 +2717,28 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>9</v>
       </c>
       <c r="U29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>5</v>
@@ -2919,10 +2904,10 @@
         <v>78.3</v>
       </c>
       <c r="N4">
-        <v>72.5</v>
+        <v>81.3</v>
       </c>
       <c r="O4">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="P4">
         <v>85</v>
@@ -2931,10 +2916,10 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>91.5</v>
+        <v>94.7</v>
       </c>
       <c r="S4">
-        <v>78.3</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2978,7 +2963,7 @@
         <v>98.3</v>
       </c>
       <c r="N5">
-        <v>87.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -2987,13 +2972,13 @@
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R5">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S5">
-        <v>98.3</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3037,7 +3022,7 @@
         <v>98.3</v>
       </c>
       <c r="N6">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -3049,10 +3034,10 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>96.59999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S6">
-        <v>98.3</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3096,7 +3081,7 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -3108,7 +3093,7 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -3155,10 +3140,10 @@
         <v>91.7</v>
       </c>
       <c r="N8">
-        <v>77.5</v>
+        <v>54.7</v>
       </c>
       <c r="O8">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="P8">
         <v>85</v>
@@ -3167,10 +3152,10 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>86.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="S8">
-        <v>91.7</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3214,7 +3199,7 @@
         <v>96.7</v>
       </c>
       <c r="N9">
-        <v>82.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -3226,10 +3211,10 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="S9">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3273,7 +3258,7 @@
         <v>91.7</v>
       </c>
       <c r="N10">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -3285,10 +3270,10 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S10">
-        <v>91.7</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3332,7 +3317,7 @@
         <v>98.3</v>
       </c>
       <c r="N11">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -3344,10 +3329,10 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="S11">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3391,7 +3376,7 @@
         <v>83.3</v>
       </c>
       <c r="N12">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -3403,10 +3388,10 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>89.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="S12">
-        <v>83.3</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3450,7 +3435,7 @@
         <v>95</v>
       </c>
       <c r="N13">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -3462,10 +3447,10 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="S13">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3509,7 +3494,7 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>92.5</v>
+        <v>87.5</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -3568,7 +3553,7 @@
         <v>93.3</v>
       </c>
       <c r="N15">
-        <v>70</v>
+        <v>81.3</v>
       </c>
       <c r="O15">
         <v>100</v>
@@ -3580,10 +3565,10 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>96.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="S15">
-        <v>93.3</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3627,7 +3612,7 @@
         <v>88.3</v>
       </c>
       <c r="N16">
-        <v>75</v>
+        <v>82.8</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -3639,10 +3624,10 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>89.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="S16">
-        <v>88.3</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3686,7 +3671,7 @@
         <v>98.3</v>
       </c>
       <c r="N17">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -3701,7 +3686,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>98.3</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3745,7 +3730,7 @@
         <v>93.3</v>
       </c>
       <c r="N18">
-        <v>82.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -3757,10 +3742,10 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>96.59999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="S18">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3804,7 +3789,7 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -3816,7 +3801,7 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -3863,7 +3848,7 @@
         <v>95</v>
       </c>
       <c r="N20">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -3875,10 +3860,10 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>96.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="S20">
-        <v>95</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3981,7 +3966,7 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O22">
         <v>100</v>
@@ -3993,7 +3978,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -4040,7 +4025,7 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="O23">
         <v>100</v>
@@ -4049,10 +4034,10 @@
         <v>95</v>
       </c>
       <c r="Q23">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -4099,7 +4084,7 @@
         <v>95</v>
       </c>
       <c r="N24">
-        <v>87.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O24">
         <v>100</v>
@@ -4111,10 +4096,10 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>93.2</v>
+        <v>94.7</v>
       </c>
       <c r="S24">
-        <v>95</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4158,7 +4143,7 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="O25">
         <v>100</v>
@@ -4167,13 +4152,13 @@
         <v>97.5</v>
       </c>
       <c r="Q25">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R25">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4217,7 +4202,7 @@
         <v>95</v>
       </c>
       <c r="N26">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -4226,13 +4211,13 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R26">
-        <v>94.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="S26">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4276,7 +4261,7 @@
         <v>96.7</v>
       </c>
       <c r="N27">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="O27">
         <v>100</v>
@@ -4291,7 +4276,7 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4335,7 +4320,7 @@
         <v>78.3</v>
       </c>
       <c r="N28">
-        <v>70</v>
+        <v>81.3</v>
       </c>
       <c r="O28">
         <v>100</v>
@@ -4347,10 +4332,10 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>86.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="S28">
-        <v>78.3</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4394,7 +4379,7 @@
         <v>86.7</v>
       </c>
       <c r="N29">
-        <v>72.5</v>
+        <v>82.8</v>
       </c>
       <c r="O29">
         <v>100</v>
@@ -4406,10 +4391,10 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>94.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="S29">
-        <v>86.7</v>
+        <v>91.7</v>
       </c>
     </row>
   </sheetData>
@@ -4475,19 +4460,19 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2">
-        <v>61.5</v>
+        <v>69.2</v>
       </c>
       <c r="G2" s="2">
-        <v>38.5</v>
+        <v>30.8</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4498,7 +4483,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
@@ -4507,19 +4492,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>84.59999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="G3" s="2">
-        <v>15.4</v>
+        <v>7.7</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4530,7 +4515,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
@@ -4539,19 +4524,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>88.5</v>
+        <v>96.2</v>
       </c>
       <c r="G4" s="2">
-        <v>11.5</v>
+        <v>3.8</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4562,7 +4547,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
@@ -4571,19 +4556,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>88.5</v>
+        <v>96.2</v>
       </c>
       <c r="G5" s="2">
-        <v>11.5</v>
+        <v>3.8</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4594,7 +4579,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
@@ -4603,19 +4588,19 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4626,7 +4611,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -4647,7 +4632,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4697,7 +4682,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4729,22 +4714,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920031</v>
+        <v>21330051920035</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4752,22 +4737,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920031</v>
+        <v>21330051920036</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4775,22 +4760,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920390</v>
+        <v>21330051920046</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4798,22 +4783,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920390</v>
+        <v>21330051920048</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
         <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4824,13 +4809,13 @@
         <v>21330051920057</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -4844,10 +4829,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920057</v>
+        <v>21330051920059</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
         <v>72</v>
@@ -4856,7 +4841,7 @@
         <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>51</v>
@@ -4867,10 +4852,10 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920063</v>
+        <v>21330051920065</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
         <v>73</v>
@@ -4879,10 +4864,10 @@
         <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4890,16 +4875,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920063</v>
+        <v>21330051920067</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -4908,144 +4893,6 @@
         <v>50</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920035</v>
-      </c>
-      <c r="B10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920036</v>
-      </c>
-      <c r="B11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920046</v>
-      </c>
-      <c r="B12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920048</v>
-      </c>
-      <c r="B13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920062</v>
-      </c>
-      <c r="B14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920065</v>
-      </c>
-      <c r="B15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHV - Estadisticos 20231.xlsx
+++ b/grupos/5ARHV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="63">
   <si>
     <t>Materia</t>
   </si>
@@ -170,18 +170,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
+    <t>Saucedo Rivalcoba Liliana Guadalupe</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>Saucedo Rivalcoba Liliana Guadalupe</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
@@ -200,73 +200,13 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>ROMANOS</t>
   </si>
   <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>TEZOCO</t>
   </si>
   <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABET</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>MICHEL</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
-  </si>
-  <si>
     <t>DANIELA</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
   </si>
 </sst>
 </file>
@@ -798,7 +738,7 @@
         <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
         <v>8</v>
@@ -875,7 +815,7 @@
         <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
         <v>9</v>
@@ -952,7 +892,7 @@
         <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
         <v>9</v>
@@ -1029,7 +969,7 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
         <v>9</v>
@@ -1106,7 +1046,7 @@
         <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <v>9</v>
@@ -1183,7 +1123,7 @@
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
         <v>8</v>
@@ -1201,7 +1141,7 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1260,7 +1200,7 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>8</v>
@@ -1278,7 +1218,7 @@
         <v>9</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1337,7 +1277,7 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
         <v>9</v>
@@ -1414,7 +1354,7 @@
         <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -1491,7 +1431,7 @@
         <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>8</v>
@@ -1568,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>10</v>
@@ -1645,7 +1585,7 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>9</v>
@@ -1722,7 +1662,7 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -1740,7 +1680,7 @@
         <v>7</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>8</v>
@@ -1799,7 +1739,7 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>8</v>
@@ -1876,7 +1816,7 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
         <v>9</v>
@@ -1894,7 +1834,7 @@
         <v>7</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -1953,7 +1893,7 @@
         <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>9</v>
@@ -2030,7 +1970,7 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
         <v>9</v>
@@ -2048,7 +1988,7 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -2107,7 +2047,7 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>9</v>
@@ -2184,7 +2124,7 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -2261,7 +2201,7 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>9</v>
@@ -2338,7 +2278,7 @@
         <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
         <v>9</v>
@@ -2356,7 +2296,7 @@
         <v>6</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2415,7 +2355,7 @@
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>9</v>
@@ -2492,7 +2432,7 @@
         <v>7</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
         <v>9</v>
@@ -2569,7 +2509,7 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
         <v>9</v>
@@ -2587,7 +2527,7 @@
         <v>7</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -2646,7 +2586,7 @@
         <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
         <v>9</v>
@@ -2664,7 +2604,7 @@
         <v>7</v>
       </c>
       <c r="V28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>8</v>
@@ -2723,7 +2663,7 @@
         <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
         <v>9</v>
@@ -2741,7 +2681,7 @@
         <v>7</v>
       </c>
       <c r="V29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -2910,7 +2850,7 @@
         <v>96.3</v>
       </c>
       <c r="P4">
-        <v>85</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -3028,7 +2968,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3087,7 +3027,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3146,7 +3086,7 @@
         <v>81.3</v>
       </c>
       <c r="P8">
-        <v>85</v>
+        <v>53.1</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3382,7 +3322,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -3441,7 +3381,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -3500,7 +3440,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -3559,7 +3499,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -3618,7 +3558,7 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -3677,7 +3617,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>90</v>
+        <v>92.2</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -3795,7 +3735,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -4031,7 +3971,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q23">
         <v>98.7</v>
@@ -4149,7 +4089,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q25">
         <v>98.7</v>
@@ -4208,7 +4148,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q26">
         <v>98.7</v>
@@ -4326,7 +4266,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -4451,7 +4391,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>50</v>
@@ -4460,19 +4400,19 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>69.2</v>
+        <v>92.3</v>
       </c>
       <c r="G2" s="2">
-        <v>30.8</v>
+        <v>7.7</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4483,7 +4423,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
@@ -4492,19 +4432,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="G3" s="2">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4515,7 +4455,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
@@ -4536,7 +4476,7 @@
         <v>3.8</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4547,7 +4487,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
@@ -4568,7 +4508,7 @@
         <v>3.8</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4682,7 +4622,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4714,185 +4654,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920035</v>
+        <v>21330051920059</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>50</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920036</v>
-      </c>
-      <c r="B3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920046</v>
-      </c>
-      <c r="B4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920048</v>
-      </c>
-      <c r="B5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920057</v>
-      </c>
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920059</v>
-      </c>
-      <c r="B7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920065</v>
-      </c>
-      <c r="B8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920067</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHV - Estadisticos 20231.xlsx
+++ b/grupos/5ARHV - Estadisticos 20231.xlsx
@@ -750,22 +750,22 @@
         <v>9</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -827,22 +827,22 @@
         <v>8</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -907,19 +907,19 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -981,16 +981,16 @@
         <v>10</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U7">
         <v>10</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1067,7 +1067,7 @@
         <v>5</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>5</v>
@@ -1135,22 +1135,22 @@
         <v>6</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1212,22 +1212,22 @@
         <v>8</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1292,19 +1292,19 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1366,22 +1366,22 @@
         <v>8</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1443,22 +1443,22 @@
         <v>8</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1532,7 +1532,7 @@
         <v>10</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1597,22 +1597,22 @@
         <v>7</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1674,22 +1674,22 @@
         <v>8</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1760,13 +1760,13 @@
         <v>10</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1828,22 +1828,22 @@
         <v>8</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1908,19 +1908,19 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1982,22 +1982,22 @@
         <v>7</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2062,19 +2062,19 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2139,19 +2139,19 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2213,22 +2213,22 @@
         <v>10</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2290,22 +2290,22 @@
         <v>7</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2367,22 +2367,22 @@
         <v>8</v>
       </c>
       <c r="T25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2444,22 +2444,22 @@
         <v>6</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2521,22 +2521,22 @@
         <v>9</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2598,22 +2598,22 @@
         <v>8</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2675,22 +2675,22 @@
         <v>8</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -4412,7 +4412,7 @@
         <v>7.7</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4444,7 +4444,7 @@
         <v>3.8</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4476,7 +4476,7 @@
         <v>3.8</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4508,7 +4508,7 @@
         <v>3.8</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4540,7 +4540,7 @@
         <v>3.8</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/5ARHV - Estadisticos 20231.xlsx
+++ b/grupos/5ARHV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="60">
   <si>
     <t>Materia</t>
   </si>
@@ -170,21 +170,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Saucedo Rivalcoba Liliana Guadalupe</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
-    <t>Saucedo Rivalcoba Liliana Guadalupe</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
@@ -198,15 +198,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
   </si>
 </sst>
 </file>
@@ -750,22 +741,22 @@
         <v>9</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -827,22 +818,22 @@
         <v>8</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -907,19 +898,19 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -981,16 +972,16 @@
         <v>10</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>10</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1067,7 +1058,7 @@
         <v>5</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>5</v>
@@ -1135,22 +1126,22 @@
         <v>6</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1212,22 +1203,22 @@
         <v>8</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1292,19 +1283,19 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1366,22 +1357,22 @@
         <v>8</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1443,22 +1434,22 @@
         <v>8</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1532,7 +1523,7 @@
         <v>10</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1597,22 +1588,22 @@
         <v>7</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1674,22 +1665,22 @@
         <v>8</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1760,13 +1751,13 @@
         <v>10</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1828,22 +1819,22 @@
         <v>8</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1908,19 +1899,19 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1982,22 +1973,22 @@
         <v>7</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2062,19 +2053,19 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2139,19 +2130,19 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2213,22 +2204,22 @@
         <v>10</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2290,22 +2281,22 @@
         <v>7</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2367,22 +2358,22 @@
         <v>8</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2444,22 +2435,22 @@
         <v>6</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2521,22 +2512,22 @@
         <v>9</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2598,22 +2589,22 @@
         <v>8</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2675,22 +2666,22 @@
         <v>8</v>
       </c>
       <c r="T29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3977,7 +3968,7 @@
         <v>98.7</v>
       </c>
       <c r="R23">
-        <v>72.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -4391,7 +4382,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>50</v>
@@ -4400,19 +4391,19 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="G2" s="2">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
       <c r="H2">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4423,7 +4414,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
@@ -4444,7 +4435,7 @@
         <v>3.8</v>
       </c>
       <c r="H3">
-        <v>9.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4455,7 +4446,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
@@ -4476,7 +4467,7 @@
         <v>3.8</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4487,7 +4478,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
@@ -4508,7 +4499,7 @@
         <v>3.8</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4519,7 +4510,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
@@ -4540,7 +4531,7 @@
         <v>3.8</v>
       </c>
       <c r="H6">
-        <v>9.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4572,7 +4563,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4622,7 +4613,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4652,29 +4643,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920059</v>
-      </c>
-      <c r="B2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
